--- a/game_config/Datas/ConfigTablePolicy.xlsx
+++ b/game_config/Datas/ConfigTablePolicy.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,6 +544,30 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MonsterConfig</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MonsterAreaConfig</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/game_config/Datas/ConfigTablePolicy.xlsx
+++ b/game_config/Datas/ConfigTablePolicy.xlsx
@@ -1,34 +1,115 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitee\TiangZ\game_config\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3E01C76-1984-4B74-9E63-2E06AB1839CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-28920" yWindow="-1320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ConfigTablePolicy" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ConfigTablePolicy" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
+  <si>
+    <t>##var</t>
+  </si>
+  <si>
+    <t>table_name</t>
+  </si>
+  <si>
+    <t>reload_mode</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>ConfigReloadMode</t>
+  </si>
+  <si>
+    <t>##group</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>配置记录类型名称</t>
+  </si>
+  <si>
+    <t>重载策略</t>
+  </si>
+  <si>
+    <t>ItemConfig</t>
+  </si>
+  <si>
+    <t>Hot</t>
+  </si>
+  <si>
+    <t>MapConfig</t>
+  </si>
+  <si>
+    <t>Cold</t>
+  </si>
+  <si>
+    <t>PlayerConfig</t>
+  </si>
+  <si>
+    <t>AoiConfig</t>
+  </si>
+  <si>
+    <t>AoiSyncTierConfig</t>
+  </si>
+  <si>
+    <t>MonsterConfig</t>
+  </si>
+  <si>
+    <t>MonsterAreaConfig</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +128,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,167 +430,117 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="27.109375" customWidth="1"/>
+    <col min="3" max="3" width="20.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>table_name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>reload_mode</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>##type</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ConfigReloadMode</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>##group</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>##</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>配置记录类型名称</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>重载策略</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>ItemConfig</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>MapConfig</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Cold</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>PlayerConfig</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>AoiConfig</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Cold</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>AoiSyncTierConfig</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Cold</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>MonsterConfig</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Cold</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>MonsterAreaConfig</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Cold</t>
-        </is>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/game_config/Datas/ConfigTablePolicy.xlsx
+++ b/game_config/Datas/ConfigTablePolicy.xlsx
@@ -1,115 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitee\TiangZ\game_config\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3E01C76-1984-4B74-9E63-2E06AB1839CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-1320" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ConfigTablePolicy" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ConfigTablePolicy" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>table_name</t>
-  </si>
-  <si>
-    <t>reload_mode</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>ConfigReloadMode</t>
-  </si>
-  <si>
-    <t>##group</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>配置记录类型名称</t>
-  </si>
-  <si>
-    <t>重载策略</t>
-  </si>
-  <si>
-    <t>ItemConfig</t>
-  </si>
-  <si>
-    <t>Hot</t>
-  </si>
-  <si>
-    <t>MapConfig</t>
-  </si>
-  <si>
-    <t>Cold</t>
-  </si>
-  <si>
-    <t>PlayerConfig</t>
-  </si>
-  <si>
-    <t>AoiConfig</t>
-  </si>
-  <si>
-    <t>AoiSyncTierConfig</t>
-  </si>
-  <si>
-    <t>MonsterConfig</t>
-  </si>
-  <si>
-    <t>MonsterAreaConfig</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -128,21 +53,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -430,117 +414,184 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.109375" customWidth="1"/>
-    <col min="3" max="3" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col width="27.109375" customWidth="1" min="2" max="2"/>
+    <col width="20.44140625" bestFit="1" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" t="s">
-        <v>14</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>table_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>reload_mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ConfigReloadMode</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>配置记录类型名称</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>重载策略</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ItemConfig</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MapConfig</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PlayerConfig</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AoiConfig</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AoiSyncTierConfig</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MonsterConfig</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MonsterAreaConfig</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BuffConfig</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/game_config/Datas/ConfigTablePolicy.xlsx
+++ b/game_config/Datas/ConfigTablePolicy.xlsx
@@ -1,40 +1,130 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitee\TiangZ\game_config\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C77B8A20-2914-40D0-A06D-59B492657DE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-1320" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ConfigTablePolicy" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ConfigTablePolicy" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
+  <si>
+    <t>##var</t>
+  </si>
+  <si>
+    <t>table_name</t>
+  </si>
+  <si>
+    <t>reload_mode</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>ConfigReloadMode</t>
+  </si>
+  <si>
+    <t>##group</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>配置记录类型名称</t>
+  </si>
+  <si>
+    <t>重载策略</t>
+  </si>
+  <si>
+    <t>ItemConfig</t>
+  </si>
+  <si>
+    <t>Hot</t>
+  </si>
+  <si>
+    <t>MapConfig</t>
+  </si>
+  <si>
+    <t>Cold</t>
+  </si>
+  <si>
+    <t>PlayerConfig</t>
+  </si>
+  <si>
+    <t>AoiConfig</t>
+  </si>
+  <si>
+    <t>AoiSyncTierConfig</t>
+  </si>
+  <si>
+    <t>MonsterConfig</t>
+  </si>
+  <si>
+    <t>MonsterAreaConfig</t>
+  </si>
+  <si>
+    <t>BuffConfig</t>
+  </si>
+  <si>
+    <t>SkillConfig</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillEffectConfig</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -53,80 +143,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -414,184 +445,142 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="27.109375" customWidth="1" min="2" max="2"/>
-    <col width="20.44140625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col min="1" max="1" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>table_name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>reload_mode</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>##type</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ConfigReloadMode</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>##group</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>##</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>配置记录类型名称</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>重载策略</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>ItemConfig</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>MapConfig</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Cold</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>PlayerConfig</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>AoiConfig</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Cold</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>AoiSyncTierConfig</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Cold</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>MonsterConfig</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Cold</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>MonsterAreaConfig</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Cold</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>BuffConfig</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/game_config/Datas/ConfigTablePolicy.xlsx
+++ b/game_config/Datas/ConfigTablePolicy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitee\TiangZ\game_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C77B8A20-2914-40D0-A06D-59B492657DE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B45D5E24-536B-48A6-8D0E-ADB2B8048600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
   <si>
     <t>##var</t>
   </si>
@@ -100,6 +100,12 @@
   <si>
     <t>SkillEffectConfig</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QuestConfig</t>
+  </si>
+  <si>
+    <t>QuestObjectiveConfig</t>
   </si>
 </sst>
 </file>
@@ -446,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.5546875" bestFit="1" customWidth="1"/>
@@ -578,6 +584,22 @@
         <v>22</v>
       </c>
     </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/game_config/Datas/ConfigTablePolicy.xlsx
+++ b/game_config/Datas/ConfigTablePolicy.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>##var</t>
   </si>
@@ -91,21 +91,21 @@
   </si>
   <si>
     <t>SkillConfig</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Hot</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>SkillEffectConfig</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>QuestConfig</t>
   </si>
   <si>
     <t>QuestObjectiveConfig</t>
+  </si>
+  <si>
+    <t>DropTableConfig</t>
   </si>
 </sst>
 </file>
@@ -452,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.5546875" bestFit="1" customWidth="1"/>
@@ -600,6 +600,14 @@
         <v>12</v>
       </c>
     </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
